--- a/output/pdf_financials_xlsx/ESPN.xlsx
+++ b/output/pdf_financials_xlsx/ESPN.xlsx
@@ -1410,25 +1410,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.089133</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.16179</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.09342499999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.075242</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.002622</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.493763</v>
       </c>
     </row>
     <row r="35">
@@ -1466,25 +1466,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.089133</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.16179</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.09342499999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.075242</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.002622</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.493763</v>
       </c>
     </row>
     <row r="37">
@@ -1802,25 +1802,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.089133</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.40081</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.167412</v>
+        <v>0.005622</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.09342499999999999</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.075242</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.002622</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.518763</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="49">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">

--- a/output/pdf_financials_xlsx/ESPN.xlsx
+++ b/output/pdf_financials_xlsx/ESPN.xlsx
@@ -3851,10 +3851,10 @@
         <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>0.477423</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>0.238373</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -9207,7 +9207,11 @@
           <t>Issue of common shares net of issue costs</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -10084,7 +10088,11 @@
           <t>Issue of common shares net of issue costs 238,373</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ESPN.xlsx
+++ b/output/pdf_financials_xlsx/ESPN.xlsx
@@ -3567,13 +3567,13 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.00781</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.003612</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -3604,7 +3604,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005874</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -3812,10 +3812,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
@@ -4286,7 +4284,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005874</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -4298,10 +4296,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.035867</v>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
@@ -4318,7 +4314,7 @@
         <v>0.032301</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.053367</v>
+        <v>-0.059241</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.09752</v>
@@ -4335,7 +4331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K181"/>
+  <dimension ref="A1:K196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7705,7 +7701,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -8046,7 +8046,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -8556,7 +8560,11 @@
           <t>Interest accretion expense</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -9621,7 +9629,11 @@
           <t>Interest accretion expense 7,810</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -11219,20 +11231,26 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Operating activities</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>For the years ended December 31, 2025 and December</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>-0.06586699999999999</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11254,34 +11272,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J135" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="K135" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>General and corporate (note 7,11) $</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0.03</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11298,41 +11322,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I136" s="5" t="n">
-        <v>0.661931</v>
-      </c>
-      <c r="J136" s="5" t="n">
-        <v>0.865682</v>
-      </c>
-      <c r="K136" s="5" t="n">
-        <v>0.668822</v>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>-0.035867</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11359,31 +11387,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K137" s="5" t="n">
-        <v>0.001244</v>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mineral property investigation expenses</t>
+          <t>Issuance of share capital (note 3)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E138" s="5" t="n">
+        <v>0.125</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11395,44 +11423,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H138" s="5" t="n">
-        <v>0.030538</v>
-      </c>
-      <c r="I138" s="5" t="n">
-        <v>0.07141599999999999</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>0.027791</v>
-      </c>
-      <c r="K138" s="5" t="n">
-        <v>0.048222</v>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Net loss before other items</t>
+          <t>Cash provided by financing activities</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.125</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11454,34 +11488,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J139" s="5" t="n">
-        <v>-0.893473</v>
-      </c>
-      <c r="K139" s="5" t="n">
-        <v>-0.718288</v>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash during the period</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>0.089133</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11508,29 +11548,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K140" s="5" t="n">
-        <v>1.274371</v>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
+          <t>Cash - beginning of period</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -11558,34 +11600,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J141" s="5" t="n">
-        <v>-0.893473</v>
-      </c>
-      <c r="K141" s="5" t="n">
-        <v>0.556083</v>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Other comprehensive income/ (loss)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Foreign currency translation gain</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash - end of period $</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>0.089133</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11602,14 +11650,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I142" s="5" t="n">
-        <v>0.013594</v>
-      </c>
-      <c r="J142" s="5" t="n">
-        <v>0.003594</v>
-      </c>
-      <c r="K142" s="5" t="n">
-        <v>0.005299</v>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -11618,14 +11672,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Other comprehensive income/ (loss)</t>
-        </is>
-      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) $</t>
+          <t>For the years ended December 31, 2025 and December</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -11655,10 +11705,10 @@
         </is>
       </c>
       <c r="J143" s="5" t="n">
-        <v>-0.889879</v>
+        <v>0.002024</v>
       </c>
       <c r="K143" s="5" t="n">
-        <v>0.561382</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="144">
@@ -11669,19 +11719,15 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Other comprehensive income/ (loss)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>General and corporate (note 7,11) $</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -11697,17 +11743,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H144" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I144" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.661931</v>
       </c>
       <c r="J144" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.865682</v>
       </c>
       <c r="K144" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.668822</v>
       </c>
     </row>
     <row r="145">
@@ -11718,15 +11766,19 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Other comprehensive income/ (loss)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -11742,17 +11794,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H145" s="5" t="n">
-        <v>56.313813</v>
-      </c>
-      <c r="I145" s="5" t="n">
-        <v>58.510159</v>
-      </c>
-      <c r="J145" s="5" t="n">
-        <v>58.510159</v>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>65.98961199999999</v>
+        <v>0.001244</v>
       </c>
     </row>
     <row r="146">
@@ -11761,10 +11819,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>For the years ended December 31, 2024 and December</t>
+          <t>Mineral property investigation expenses</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -11783,21 +11845,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H146" s="5" t="n">
+        <v>0.030538</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.07141599999999999</v>
       </c>
       <c r="J146" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.027791</v>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>0.048222</v>
       </c>
     </row>
     <row r="147">
@@ -11813,12 +11871,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Net Loss</t>
+          <t>Net loss before other items</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -11841,16 +11899,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="5" t="n">
-        <v>-0.733347</v>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J147" s="5" t="n">
         <v>-0.893473</v>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K147" s="5" t="n">
+        <v>-0.718288</v>
       </c>
     </row>
     <row r="148">
@@ -11861,12 +11919,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Other comprehensive income/ (loss)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Comprehensive loss $</t>
+          <t>Gain on settlement of debt</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -11885,19 +11943,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H148" s="5" t="n">
-        <v>-1.500141</v>
-      </c>
-      <c r="I148" s="5" t="n">
-        <v>-0.719753</v>
-      </c>
-      <c r="J148" s="5" t="n">
-        <v>-0.889879</v>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>1.274371</v>
       </c>
     </row>
     <row r="149">
@@ -11906,13 +11968,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>For the years ended December 31, 2023 and December</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
+          <t>Net income (loss)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -11928,21 +11998,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H149" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="I149" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="n">
+        <v>-0.893473</v>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>0.556083</v>
       </c>
     </row>
     <row r="150">
@@ -11953,12 +12023,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income/ (loss)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>General and corporate (note 8) $</t>
+          <t>Foreign currency translation gain</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -11977,21 +12047,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H150" s="5" t="n">
-        <v>0.836318</v>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I150" s="5" t="n">
-        <v>0.661931</v>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.013594</v>
+      </c>
+      <c r="J150" s="5" t="n">
+        <v>0.003594</v>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>0.005299</v>
       </c>
     </row>
     <row r="151">
@@ -12002,19 +12070,15 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income/ (loss)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Comprehensive income (loss) $</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -12025,24 +12089,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G151" s="5" t="n">
-        <v>1.075003</v>
-      </c>
-      <c r="H151" s="5" t="n">
-        <v>0.866856</v>
-      </c>
-      <c r="I151" s="5" t="n">
-        <v>0.733347</v>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="n">
+        <v>-0.889879</v>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>0.561382</v>
       </c>
     </row>
     <row r="152">
@@ -12053,15 +12119,19 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Other comprehensive income/ (loss)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Listing expense (note 5)</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -12078,22 +12148,16 @@
         </is>
       </c>
       <c r="H152" s="5" t="n">
-        <v>-0.646347</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3e-08</v>
+      </c>
+      <c r="I152" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="J152" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>1e-08</v>
       </c>
     </row>
     <row r="153">
@@ -12104,12 +12168,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Other comprehensive income/ (loss)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Gain (loss) on settlement of debt (note 8)</t>
+          <t>Weighted average number of common shares outstanding, basic and diluted</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -12129,22 +12193,16 @@
         </is>
       </c>
       <c r="H153" s="5" t="n">
-        <v>-0.002927</v>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>56.313813</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>58.510159</v>
+      </c>
+      <c r="J153" s="5" t="n">
+        <v>58.510159</v>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>65.98961199999999</v>
       </c>
     </row>
     <row r="154">
@@ -12153,21 +12211,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>For the years ended December 31, 2024 and December</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -12183,16 +12233,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H154" s="5" t="n">
-        <v>-1.51613</v>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I154" s="5" t="n">
-        <v>-0.733347</v>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="J154" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -12208,15 +12258,19 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Other comprehensive income/ (loss)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Foreign currency translation gain(loss)</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
+          <t>Net Loss</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -12232,16 +12286,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H155" s="5" t="n">
-        <v>0.015989</v>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I155" s="5" t="n">
-        <v>0.013594</v>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.733347</v>
+      </c>
+      <c r="J155" s="5" t="n">
+        <v>-0.893473</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -12257,12 +12311,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income/ (loss)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>General and corporate (note 8) $ 836,318 $</t>
+          <t>Comprehensive loss $</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -12276,21 +12330,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G156" s="5" t="n">
-        <v>0.998871</v>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H156" s="5" t="n">
-        <v>0.252697</v>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.500141</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>-0.719753</v>
+      </c>
+      <c r="J156" s="5" t="n">
+        <v>-0.889879</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -12304,14 +12356,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mineral property investigation expenses 30,538</t>
+          <t>For the years ended December 31, 2023 and December</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -12325,16 +12373,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G157" s="5" t="n">
-        <v>0.07613200000000001</v>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H157" s="5" t="n">
-        <v>0.006927</v>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002022</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -12355,12 +12403,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Listing expense (note 5) (646,347)</t>
+          <t>General and corporate (note 8) $</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -12379,15 +12427,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H158" s="5" t="n">
+        <v>0.836318</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>0.661931</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -12408,15 +12452,19 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Gain (loss) on settlement of debt (note 8) (2,927)</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -12427,18 +12475,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G159" s="5" t="n">
+        <v>1.075003</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>0.08577</v>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.866856</v>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>0.733347</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -12464,7 +12508,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Impairment of exploration assets (note 6) -</t>
+          <t>Listing expense (note 5)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -12478,13 +12522,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G160" s="5" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>-0.646347</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -12515,7 +12559,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Net loss $ (1,516,130) $</t>
+          <t>Gain (loss) on settlement of debt (note 8)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -12529,11 +12573,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G161" s="5" t="n">
-        <v>-1.305003</v>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H161" s="5" t="n">
-        <v>-0.173854</v>
+        <v>-0.002927</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -12559,15 +12605,19 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Other comprehensive income/ (loss)</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Foreign currency translation gain(loss) 15,989</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -12578,16 +12628,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G162" s="5" t="n">
-        <v>-0.023046</v>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H162" s="5" t="n">
-        <v>-0.002717</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.51613</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>-0.733347</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -12613,7 +12663,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Comprehensive loss $ (1,500,141) $</t>
+          <t>Foreign currency translation gain(loss)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -12627,16 +12677,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G163" s="5" t="n">
-        <v>-1.328049</v>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H163" s="5" t="n">
-        <v>-0.176571</v>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.015989</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>0.013594</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -12657,12 +12707,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Other comprehensive income/ (loss)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $ (0.03) $</t>
+          <t>General and corporate (note 8) $ 836,318 $</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -12677,10 +12727,10 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.998871</v>
       </c>
       <c r="H164" s="5" t="n">
-        <v>0</v>
+        <v>0.252697</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -12706,12 +12756,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted 56,313,813</t>
+          <t>Mineral property investigation expenses 30,538</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12726,10 +12776,10 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>39.706977</v>
+        <v>0.07613200000000001</v>
       </c>
       <c r="H165" s="5" t="n">
-        <v>44.676826</v>
+        <v>0.006927</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -12755,20 +12805,24 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Professional and administrative</t>
+          <t>Listing expense (note 5) (646,347)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" s="5" t="n">
-        <v>0.06586699999999999</v>
-      </c>
-      <c r="F166" s="5" t="n">
-        <v>0.101459</v>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -12804,12 +12858,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Stock-based compensation 5</t>
+          <t>Gain (loss) on settlement of debt (note 8) (2,927)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -12818,18 +12872,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F167" s="5" t="n">
-        <v>0.067258</v>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H167" s="5" t="n">
+        <v>0.08577</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -12855,29 +12909,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E168" s="5" t="n">
-        <v>-0.06586699999999999</v>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>-0.168717</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Impairment of exploration assets (note 6) -</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>-0.23</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -12908,12 +12960,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average number of shares: 4</t>
+          <t>Net loss $ (1,516,130) $</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -12922,18 +12974,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F169" s="5" t="n">
-        <v>4.191781</v>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>-1.305003</v>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>-0.173854</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -12959,34 +13009,30 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income/ (loss)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share: 4</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E170" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Foreign currency translation gain(loss) 15,989</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>-0.023046</v>
+      </c>
+      <c r="H170" s="5" t="n">
+        <v>-0.002717</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -13012,30 +13058,30 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Other comprehensive income/ (loss)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Balance at October</t>
+          <t>Comprehensive loss $ (1,500,141) $</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F171" s="5" t="n">
-        <v>2.2e-05</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>-1.328049</v>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>-0.176571</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -13061,12 +13107,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Other comprehensive income/ (loss)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>(Inception) - - - -</t>
+          <t>Loss per share, basic and diluted $ (0.03) $</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -13080,15 +13126,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G172" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -13114,32 +13156,30 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Common shares issued for cash 2,500,000 125,000 - -</t>
+          <t>Weighted average number of common shares outstanding, basic and diluted 56,313,813</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" s="5" t="n">
-        <v>0.125</v>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G173" s="5" t="n">
+        <v>39.706977</v>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>44.676826</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -13165,24 +13205,20 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss - - - -</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Professional and administrative</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" s="5" t="n">
-        <v>-0.06586699999999999</v>
+        <v>0.06586699999999999</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>-0.06586699999999999</v>
+        <v>0.101459</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -13218,20 +13254,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2018 2,500,000 125,000 - -</t>
+          <t>Stock-based compensation 5</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" s="5" t="n">
-        <v>0.059133</v>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F175" s="5" t="n">
-        <v>-0.06586699999999999</v>
+        <v>0.067258</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -13267,22 +13305,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Common shares issued for cash 5,000,000 500,000 - -</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>Net Loss and Comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E176" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.06586699999999999</v>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>-0.168717</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -13318,22 +13358,22 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Share issue costs - (80,004) - -</t>
+          <t>Basic and diluted weighted average number of shares: 4</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" s="5" t="n">
-        <v>-0.08000400000000001</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="n">
+        <v>4.191781</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -13369,24 +13409,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Broker warrants issued - (26,449) - 26,449</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted loss per share: 4</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -13427,17 +13467,15 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Stock-based compensation - - 67,258 -</t>
+          <t>Balance at October</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" s="5" t="n">
-        <v>0.067258</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002018</v>
+      </c>
+      <c r="F179" s="5" t="n">
+        <v>2.2e-05</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -13478,19 +13516,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Net and Comprehensive loss - - - -</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E180" s="5" t="n">
-        <v>-0.168717</v>
-      </c>
-      <c r="F180" s="5" t="n">
-        <v>-0.168717</v>
+          <t>(Inception) - - - -</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -13531,37 +13569,816 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2019 7,500,000 518,547 67,258 26,449</t>
+          <t>Common shares issued for cash 2,500,000 125,000 - -</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" s="5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss - - - -</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="n">
+        <v>-0.06586699999999999</v>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>-0.06586699999999999</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Balance at December 31, 2018 2,500,000 125,000 - -</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" s="5" t="n">
+        <v>0.059133</v>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>-0.06586699999999999</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Common shares issued for cash 5,000,000 500,000 - -</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Share issue costs - (80,004) - -</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" s="5" t="n">
+        <v>-0.08000400000000001</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Broker warrants issued - (26,449) - 26,449</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Stock-based compensation - - 67,258 -</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" s="5" t="n">
+        <v>0.067258</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Net and Comprehensive loss - - - -</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="n">
+        <v>-0.168717</v>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>-0.168717</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Balance at December 31, 2019 7,500,000 518,547 67,258 26,449</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" s="5" t="n">
         <v>0.37767</v>
       </c>
-      <c r="F181" s="5" t="n">
+      <c r="F189" s="5" t="n">
         <v>-0.234584</v>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Professional fees and administration $</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" s="5" t="n">
+        <v>-0.06586699999999999</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="n">
+        <v>-0.06586699999999999</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share (note 3) $</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Shares                    ($)                  ($)                    ($)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Balance – beginning of period - - -</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Shares                    ($)                  ($)                    ($)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Issuance of common shares (note 3) 2,500,000 125,000 -</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" s="5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Shares                    ($)                  ($)                    ($)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Loss for the period - - (65,867)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" s="5" t="n">
+        <v>-0.06586699999999999</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Shares                    ($)                  ($)                    ($)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Balance – end of period 2,500,000 125,000 (65,867)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" s="5" t="n">
+        <v>0.059133</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
         <is>
           <t>-</t>
         </is>
